--- a/diseases/d236/2020-2025.xlsx
+++ b/diseases/d236/2020-2025.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>77</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>21.00301679695811</v>
       </c>
@@ -1410,9 +1407,6 @@
       <c r="O5" t="n">
         <v>214</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>3.978232376546759</v>
       </c>
@@ -1806,9 +1800,6 @@
       <c r="O7" t="n">
         <v>307</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>2.965127445185828</v>
       </c>
@@ -2202,9 +2193,6 @@
       <c r="O9" t="n">
         <v>227</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>4.219900698486515</v>
       </c>
@@ -2598,9 +2586,6 @@
       <c r="O11" t="n">
         <v>346</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>3.341804873075885</v>
       </c>
@@ -2994,9 +2979,6 @@
       <c r="O13" t="n">
         <v>165</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>3.067328701543062</v>
       </c>
@@ -3390,9 +3372,6 @@
       <c r="O15" t="n">
         <v>311</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>3.003761027533526</v>
       </c>
@@ -3786,9 +3765,6 @@
       <c r="O17" t="n">
         <v>117</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>2.175014897457807</v>
       </c>
@@ -4182,9 +4158,6 @@
       <c r="O19" t="n">
         <v>209</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>2.018604677667225</v>
       </c>
@@ -4578,9 +4551,6 @@
       <c r="O21" t="n">
         <v>122</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>2.267964252050021</v>
       </c>
@@ -4974,9 +4944,6 @@
       <c r="O23" t="n">
         <v>192</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>1.854411952689508</v>
       </c>
@@ -5370,9 +5337,6 @@
       <c r="O25" t="n">
         <v>174</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>3.234637539809047</v>
       </c>
@@ -5766,9 +5730,6 @@
       <c r="O27" t="n">
         <v>232</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>2.240747776166489</v>
       </c>
@@ -6162,9 +6123,6 @@
       <c r="O29" t="n">
         <v>145</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>2.695531283174206</v>
       </c>
@@ -6558,9 +6516,6 @@
       <c r="O31" t="n">
         <v>232</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>2.240747776166489</v>
       </c>
@@ -6954,9 +6909,6 @@
       <c r="O33" t="n">
         <v>157</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>2.918609734195519</v>
       </c>
@@ -7350,9 +7302,6 @@
       <c r="O35" t="n">
         <v>254</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>2.453232479078829</v>
       </c>
@@ -7746,9 +7695,6 @@
       <c r="O37" t="n">
         <v>141</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>2.621171799500434</v>
       </c>
@@ -8142,9 +8088,6 @@
       <c r="O39" t="n">
         <v>277</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>2.675375577578093</v>
       </c>
@@ -8538,9 +8481,6 @@
       <c r="O41" t="n">
         <v>181</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>3.364766636238147</v>
       </c>
@@ -8934,9 +8874,6 @@
       <c r="O43" t="n">
         <v>274</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>2.646400390817319</v>
       </c>
@@ -9330,9 +9267,6 @@
       <c r="O45" t="n">
         <v>155</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>2.881429992358634</v>
       </c>
@@ -9726,9 +9660,6 @@
       <c r="O47" t="n">
         <v>242</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>2.337331732035734</v>
       </c>
@@ -10122,9 +10053,6 @@
       <c r="O49" t="n">
         <v>123</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>2.286554122968464</v>
       </c>
@@ -10518,9 +10446,6 @@
       <c r="O51" t="n">
         <v>235</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>2.269722962927263</v>
       </c>
@@ -10914,9 +10839,6 @@
       <c r="O53" t="n">
         <v>106</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>28.4454176713132</v>
       </c>
@@ -11559,9 +11481,6 @@
       <c r="O56" t="n">
         <v>143</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>2.644186520177501</v>
       </c>
@@ -11955,9 +11874,6 @@
       <c r="O58" t="n">
         <v>179</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>1.718488289054339</v>
       </c>
@@ -12351,9 +12267,6 @@
       <c r="O60" t="n">
         <v>108</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>1.997008001252937</v>
       </c>
@@ -12747,9 +12660,6 @@
       <c r="O62" t="n">
         <v>211</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>2.025704072572433</v>
       </c>
@@ -13143,9 +13053,6 @@
       <c r="O64" t="n">
         <v>150</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>2.773622223962414</v>
       </c>
@@ -13539,9 +13446,6 @@
       <c r="O66" t="n">
         <v>231</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>2.217713937271241</v>
       </c>
@@ -13935,9 +13839,6 @@
       <c r="O68" t="n">
         <v>122</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>2.255879408822763</v>
       </c>
@@ -14331,9 +14232,6 @@
       <c r="O70" t="n">
         <v>185</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>1.776091248463981</v>
       </c>
@@ -14727,9 +14625,6 @@
       <c r="O72" t="n">
         <v>94</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>1.738136593683113</v>
       </c>
@@ -15123,9 +15018,6 @@
       <c r="O74" t="n">
         <v>190</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>1.824093714638683</v>
       </c>
@@ -15519,9 +15411,6 @@
       <c r="O76" t="n">
         <v>155</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>2.866076298094494</v>
       </c>
@@ -15915,9 +15804,6 @@
       <c r="O78" t="n">
         <v>200</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>1.920098646988088</v>
       </c>
@@ -16311,9 +16197,6 @@
       <c r="O80" t="n">
         <v>129</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>2.385315112607675</v>
       </c>
@@ -16707,9 +16590,6 @@
       <c r="O82" t="n">
         <v>242</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>2.323319362855586</v>
       </c>
@@ -17103,9 +16983,6 @@
       <c r="O84" t="n">
         <v>187</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>3.457782372539808</v>
       </c>
@@ -17499,9 +17376,6 @@
       <c r="O86" t="n">
         <v>254</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>2.438525281674871</v>
       </c>
@@ -17895,9 +17769,6 @@
       <c r="O88" t="n">
         <v>170</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>3.143438520490735</v>
       </c>
@@ -18291,9 +18162,6 @@
       <c r="O90" t="n">
         <v>338</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>3.244966713409868</v>
       </c>
@@ -18687,9 +18555,6 @@
       <c r="O92" t="n">
         <v>174</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>3.2174017797964</v>
       </c>
@@ -19083,9 +18948,6 @@
       <c r="O94" t="n">
         <v>308</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>2.956951916361655</v>
       </c>
@@ -19479,9 +19341,6 @@
       <c r="O96" t="n">
         <v>164</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>3.032493631532239</v>
       </c>
@@ -19875,9 +19734,6 @@
       <c r="O98" t="n">
         <v>272</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>2.611334159903799</v>
       </c>
@@ -20271,9 +20127,6 @@
       <c r="O100" t="n">
         <v>156</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>2.88456711292091</v>
       </c>
@@ -20667,9 +20520,6 @@
       <c r="O102" t="n">
         <v>275</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>2.640135639608621</v>
       </c>
@@ -21063,9 +20913,6 @@
       <c r="O104" t="n">
         <v>78</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>20.50713082892189</v>
       </c>
@@ -21469,9 +21316,6 @@
       <c r="O106" t="n">
         <v>146</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>2.675560032740792</v>
       </c>
@@ -21865,9 +21709,6 @@
       <c r="O108" t="n">
         <v>281</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>2.679421603461241</v>
       </c>
@@ -22261,9 +22102,6 @@
       <c r="O110" t="n">
         <v>139</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>2.547279757198425</v>
       </c>
@@ -22657,9 +22495,6 @@
       <c r="O112" t="n">
         <v>242</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>2.307544583763773</v>
       </c>
@@ -23053,9 +22888,6 @@
       <c r="O114" t="n">
         <v>119</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>2.180764684220234</v>
       </c>
@@ -23449,9 +23281,6 @@
       <c r="O116" t="n">
         <v>289</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>2.755704069040208</v>
       </c>
@@ -23845,9 +23674,6 @@
       <c r="O118" t="n">
         <v>122</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>2.235741945166963</v>
       </c>
@@ -24241,9 +24067,6 @@
       <c r="O120" t="n">
         <v>212</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>2.021485337842644</v>
       </c>
@@ -24637,9 +24460,6 @@
       <c r="O122" t="n">
         <v>145</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>2.657234279091882</v>
       </c>
@@ -25033,9 +24853,6 @@
       <c r="O124" t="n">
         <v>269</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>2.564997905092789</v>
       </c>
@@ -25429,9 +25246,6 @@
       <c r="O126" t="n">
         <v>168</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>3.078726613016801</v>
       </c>
@@ -25825,9 +25639,6 @@
       <c r="O128" t="n">
         <v>291</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>2.77477468543495</v>
       </c>
@@ -26221,9 +26032,6 @@
       <c r="O130" t="n">
         <v>142</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>2.602257018145153</v>
       </c>
@@ -26617,9 +26425,6 @@
       <c r="O132" t="n">
         <v>269</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>2.564997905092789</v>
       </c>
@@ -27013,9 +26818,6 @@
       <c r="O134" t="n">
         <v>233</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>4.269900600195921</v>
       </c>
@@ -27409,9 +27211,6 @@
       <c r="O136" t="n">
         <v>269</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>2.564997905092789</v>
       </c>
@@ -27805,9 +27604,6 @@
       <c r="O138" t="n">
         <v>240</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>4.398180875738287</v>
       </c>
@@ -28201,9 +27997,6 @@
       <c r="O140" t="n">
         <v>334</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>3.184792937921902</v>
       </c>
@@ -28597,9 +28390,6 @@
       <c r="O142" t="n">
         <v>215</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>3.940037034515549</v>
       </c>
@@ -28993,9 +28783,6 @@
       <c r="O144" t="n">
         <v>284</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>2.708027528053353</v>
       </c>
@@ -29389,9 +29176,6 @@
       <c r="O146" t="n">
         <v>213</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>3.90338552721773</v>
       </c>
@@ -29785,9 +29569,6 @@
       <c r="O148" t="n">
         <v>299</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>2.851057151013918</v>
       </c>
@@ -30181,9 +29962,6 @@
       <c r="O150" t="n">
         <v>194</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>3.555196207888449</v>
       </c>
@@ -30577,9 +30355,6 @@
       <c r="O152" t="n">
         <v>292</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>2.784309993632321</v>
       </c>
@@ -30973,9 +30748,6 @@
       <c r="O154" t="n">
         <v>156</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>40.25209162511369</v>
       </c>
@@ -31379,9 +31151,6 @@
       <c r="O156" t="n">
         <v>186</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>3.370073781061526</v>
       </c>
@@ -31775,9 +31544,6 @@
       <c r="O158" t="n">
         <v>279</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>2.644175317732257</v>
       </c>
@@ -32171,9 +31937,6 @@
       <c r="O160" t="n">
         <v>186</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>3.370073781061526</v>
       </c>
@@ -32567,9 +32330,6 @@
       <c r="O162" t="n">
         <v>240</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>2.274559413103016</v>
       </c>
@@ -32963,9 +32723,6 @@
       <c r="O164" t="n">
         <v>217</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>3.93175274457178</v>
       </c>
@@ -33359,9 +33116,6 @@
       <c r="O166" t="n">
         <v>275</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>2.60626599418054</v>
       </c>
@@ -33755,9 +33509,6 @@
       <c r="O168" t="n">
         <v>177</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>3.20700569488113</v>
       </c>
@@ -34151,9 +33902,6 @@
       <c r="O170" t="n">
         <v>235</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>2.22717275866337</v>
       </c>
@@ -34547,9 +34295,6 @@
       <c r="O172" t="n">
         <v>190</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>3.442548486030591</v>
       </c>
@@ -34943,9 +34688,6 @@
       <c r="O174" t="n">
         <v>257</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>2.435674038197813</v>
       </c>
@@ -35339,9 +35081,6 @@
       <c r="O176" t="n">
         <v>221</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>4.004227449540846</v>
       </c>
@@ -35735,9 +35474,6 @@
       <c r="O178" t="n">
         <v>286</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>2.710516633947762</v>
       </c>
@@ -36131,9 +35867,6 @@
       <c r="O180" t="n">
         <v>159</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>2.880869522520337</v>
       </c>
@@ -36527,9 +36260,6 @@
       <c r="O182" t="n">
         <v>251</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>2.378810052870238</v>
       </c>
@@ -36923,9 +36653,6 @@
       <c r="O184" t="n">
         <v>284</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>5.14570405280362</v>
       </c>
@@ -37319,9 +37046,6 @@
       <c r="O186" t="n">
         <v>386</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>3.658249722740685</v>
       </c>
@@ -37715,9 +37439,6 @@
       <c r="O188" t="n">
         <v>268</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>4.85580523292736</v>
       </c>
@@ -38111,9 +37832,6 @@
       <c r="O190" t="n">
         <v>426</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>4.037342958257854</v>
       </c>
@@ -38507,9 +38225,6 @@
       <c r="O192" t="n">
         <v>237</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>4.294126269417106</v>
       </c>
@@ -38903,9 +38618,6 @@
       <c r="O194" t="n">
         <v>350</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>3.317065810775232</v>
       </c>
@@ -39299,9 +39011,6 @@
       <c r="O196" t="n">
         <v>251</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>4.547787736808834</v>
       </c>
@@ -39695,9 +39404,6 @@
       <c r="O198" t="n">
         <v>297</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>2.814767273714983</v>
       </c>
@@ -40091,9 +39797,6 @@
       <c r="O200" t="n">
         <v>206</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>3.732447305906852</v>
       </c>
@@ -40487,9 +40190,6 @@
       <c r="O202" t="n">
         <v>263</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>2.492538023525389</v>
       </c>
@@ -40883,9 +40583,6 @@
       <c r="O204" t="n">
         <v>126</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>32.02883612039284</v>
       </c>
@@ -41289,9 +40986,6 @@
       <c r="O206" t="n">
         <v>230</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>4.124332485753121</v>
       </c>
@@ -41685,9 +41379,6 @@
       <c r="O208" t="n">
         <v>333</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>3.13943651734105</v>
       </c>
@@ -42081,9 +41772,6 @@
       <c r="O210" t="n">
         <v>233</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>4.178128126871639</v>
       </c>
@@ -42477,9 +42165,6 @@
       <c r="O212" t="n">
         <v>331</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>3.120581042762425</v>
       </c>
@@ -42873,9 +42558,6 @@
       <c r="O214" t="n">
         <v>176</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>3.15601094561978</v>
       </c>
@@ -43269,9 +42951,6 @@
       <c r="O216" t="n">
         <v>370</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>3.488262797045611</v>
       </c>
@@ -43665,9 +43344,6 @@
       <c r="O218" t="n">
         <v>266</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>4.769880179175348</v>
       </c>
@@ -44061,9 +43737,6 @@
       <c r="O220" t="n">
         <v>280</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>2.639766441007489</v>
       </c>
@@ -44457,9 +44130,6 @@
       <c r="O222" t="n">
         <v>230</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>4.124332485753121</v>
       </c>
@@ -44853,9 +44523,6 @@
       <c r="O224" t="n">
         <v>271</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>2.554916805403677</v>
       </c>
@@ -45249,9 +44916,6 @@
       <c r="O226" t="n">
         <v>221</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>3.962945562397564</v>
       </c>
@@ -45645,9 +45309,6 @@
       <c r="O228" t="n">
         <v>241</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>2.272084686724304</v>
       </c>
@@ -46041,9 +45702,6 @@
       <c r="O230" t="n">
         <v>258</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>4.626425136192632</v>
       </c>
@@ -46437,9 +46095,6 @@
       <c r="O232" t="n">
         <v>343</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>3.233713890234175</v>
       </c>
@@ -46833,9 +46488,6 @@
       <c r="O234" t="n">
         <v>319</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>5.720269838935851</v>
       </c>
@@ -47229,9 +46881,6 @@
       <c r="O236" t="n">
         <v>352</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>3.318563525837987</v>
       </c>
@@ -47625,9 +47274,6 @@
       <c r="O238" t="n">
         <v>293</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>5.254040949242019</v>
       </c>
@@ -48021,9 +47667,6 @@
       <c r="O240" t="n">
         <v>423</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>3.987932873379171</v>
       </c>
@@ -48417,9 +48060,6 @@
       <c r="O242" t="n">
         <v>254</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>4.554697614701273</v>
       </c>
@@ -48813,9 +48453,6 @@
       <c r="O244" t="n">
         <v>348</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>3.280852576680737</v>
       </c>
@@ -49209,9 +48846,6 @@
       <c r="O246" t="n">
         <v>284</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>5.092654025886462</v>
       </c>
@@ -49605,9 +49239,6 @@
       <c r="O248" t="n">
         <v>343</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>3.233713890234175</v>
       </c>
@@ -50001,9 +49632,6 @@
       <c r="O250" t="n">
         <v>228</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>4.088468725007442</v>
       </c>
@@ -50397,9 +50025,6 @@
       <c r="O252" t="n">
         <v>302</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>2.847176661372364</v>
       </c>
@@ -50793,9 +50418,6 @@
       <c r="O254" t="n">
         <v>148</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>37.16109333962729</v>
       </c>
@@ -51199,9 +50821,6 @@
       <c r="O256" t="n">
         <v>247</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>4.392617486067667</v>
       </c>
@@ -51595,9 +51214,6 @@
       <c r="O258" t="n">
         <v>369</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>3.462632146570122</v>
       </c>
@@ -51991,9 +51607,6 @@
       <c r="O260" t="n">
         <v>244</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>4.339265856682229</v>
       </c>
@@ -52387,9 +52000,6 @@
       <c r="O262" t="n">
         <v>340</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>3.190501164861359</v>
       </c>
@@ -52783,9 +52393,6 @@
       <c r="O264" t="n">
         <v>273</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>4.85499827407479</v>
       </c>
@@ -53179,9 +52786,6 @@
       <c r="O266" t="n">
         <v>337</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>3.162349683994936</v>
       </c>
@@ -53575,9 +53179,6 @@
       <c r="O268" t="n">
         <v>246</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>4.374833609605854</v>
       </c>
@@ -53971,9 +53572,6 @@
       <c r="O270" t="n">
         <v>313</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>2.937137837063545</v>
       </c>
@@ -54367,9 +53965,6 @@
       <c r="O272" t="n">
         <v>246</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>4.374833609605854</v>
       </c>
@@ -54763,9 +54358,6 @@
       <c r="O274" t="n">
         <v>325</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>3.04974376052924</v>
       </c>
@@ -55159,9 +54751,6 @@
       <c r="O276" t="n">
         <v>229</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>4.072507709755043</v>
       </c>
@@ -55555,9 +55144,6 @@
       <c r="O278" t="n">
         <v>294</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>2.758845124909528</v>
       </c>
@@ -55951,9 +55537,6 @@
       <c r="O280" t="n">
         <v>234</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>4.161427092064105</v>
       </c>
@@ -56347,9 +55930,6 @@
       <c r="O282" t="n">
         <v>350</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>3.284339434416105</v>
       </c>
@@ -56743,9 +56323,6 @@
       <c r="O284" t="n">
         <v>298</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>5.2995951856201</v>
       </c>
@@ -57139,9 +56716,6 @@
       <c r="O286" t="n">
         <v>378</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>3.547086589169393</v>
       </c>
@@ -57535,9 +57109,6 @@
       <c r="O288" t="n">
         <v>350</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>6.224356761634345</v>
       </c>
@@ -57931,9 +57502,6 @@
       <c r="O290" t="n">
         <v>399</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>3.74414695523436</v>
       </c>
@@ -58327,9 +57895,6 @@
       <c r="O292" t="n">
         <v>331</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>5.88646310885991</v>
       </c>
@@ -58723,9 +58288,6 @@
       <c r="O294" t="n">
         <v>370</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>3.472015973525597</v>
       </c>
@@ -59119,9 +58681,6 @@
       <c r="O296" t="n">
         <v>250</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>4.445969115453104</v>
       </c>
@@ -59515,9 +59074,6 @@
       <c r="O298" t="n">
         <v>338</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>3.17173351095041</v>
       </c>
@@ -59911,9 +59467,6 @@
       <c r="O300" t="n">
         <v>244</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>4.339265856682229</v>
       </c>
@@ -60306,9 +59859,6 @@
       </c>
       <c r="O302" t="n">
         <v>333</v>
-      </c>
-      <c r="Q302" t="n">
-        <v>0</v>
       </c>
       <c r="R302" t="n">
         <v>3.124814376173037</v>
